--- a/dcf/NEE.xlsx
+++ b/dcf/NEE.xlsx
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1109,25 +1109,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.04653110094139964</v>
+        <v>0.04654830086232972</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.05153110094139964</v>
+        <v>0.05154830086232971</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.05653110094139965</v>
+        <v>0.05654830086232972</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.06153110094139964</v>
+        <v>0.06154830086232971</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.06653110094139965</v>
+        <v>0.06654830086232971</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.07153110094139964</v>
+        <v>0.07154830086232972</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.07653110094139964</v>
+        <v>0.07654830086232972</v>
       </c>
     </row>
     <row r="5">
@@ -1135,25 +1135,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>89.65032129774201</v>
+        <v>89.63144071564811</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>84.29511007846681</v>
+        <v>84.27714167594978</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>79.19788001365073</v>
+        <v>79.18077466154944</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>74.34477183985553</v>
+        <v>74.32848329442827</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>69.72273830393152</v>
+        <v>69.70722302413571</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>65.31949286295006</v>
+        <v>65.30470984010745</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>61.12346185263909</v>
+        <v>61.10937245158744</v>
       </c>
     </row>
     <row r="6">
@@ -1161,25 +1161,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>99.81088283530505</v>
+        <v>99.79033249816332</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>93.98274760272673</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>88.43669446464784</v>
+        <v>93.96319473342682</v>
+      </c>
+      <c r="D6" s="53" t="n">
+        <v>88.41808520366354</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>83.15753048004328</v>
+        <v>83.13981413618025</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>78.13095430201003</v>
+        <v>78.11408315154701</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>73.34349978687852</v>
+        <v>73.32742888633504</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>68.78248341914596</v>
+        <v>68.76717043068591</v>
       </c>
     </row>
     <row r="7">
@@ -1187,25 +1187,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>109.9714443728681</v>
+        <v>109.9492242806785</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>103.6703851269867</v>
+        <v>103.6492477909038</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>97.67550891564498</v>
+        <v>97.65539574577768</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>91.97028912023104</v>
+        <v>91.95114497793223</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>86.53917030008853</v>
+        <v>86.52094327895828</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>81.36750671080702</v>
+        <v>81.35014793256259</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>76.44150498565283</v>
+        <v>76.42496840978437</v>
       </c>
     </row>
     <row r="8">
@@ -1213,25 +1213,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>120.1320059104312</v>
+        <v>120.1081160631937</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>113.3580226512465</v>
+        <v>113.3353008483809</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>106.9143233666421</v>
+        <v>106.8927062878918</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>100.7830477604188</v>
+        <v>100.7624758196842</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>94.94738629816698</v>
+        <v>94.92780340636955</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>89.39151363473547</v>
+        <v>89.37286697879016</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>84.10052655215968</v>
+        <v>84.08276638888283</v>
       </c>
     </row>
     <row r="9">
@@ -1239,25 +1239,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>130.2925674479942</v>
+        <v>130.2670078457089</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>123.0456601755065</v>
+        <v>123.0213539058579</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>116.1531378176392</v>
+        <v>116.1300168300059</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>109.5958064006065</v>
+        <v>109.5738066614361</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>103.3556022962455</v>
+        <v>103.3346635337808</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>97.41552055866394</v>
+        <v>97.39558602501772</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>91.75954811866653</v>
+        <v>91.74056436798129</v>
       </c>
     </row>
     <row r="10">
@@ -1265,25 +1265,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>140.4531289855573</v>
+        <v>140.4258996282241</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>132.7332976997664</v>
+        <v>132.7074069633349</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>125.3919522686363</v>
+        <v>125.36732737212</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>118.4085650407943</v>
+        <v>118.3851375031881</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>111.763818294324</v>
+        <v>111.7415236611921</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>105.4395274825924</v>
+        <v>105.4183050712453</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>99.41856968517338</v>
+        <v>99.39836234707977</v>
       </c>
     </row>
     <row r="11">
@@ -1291,25 +1291,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>150.6136905231203</v>
+        <v>150.5847914107393</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>142.4209352240263</v>
+        <v>142.393460020812</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>134.6307667196334</v>
+        <v>134.6046379142342</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>127.2213236809821</v>
+        <v>127.1964683449401</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>120.1720342924024</v>
+        <v>120.1483837886034</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>113.4635344065209</v>
+        <v>113.4410241174729</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>107.0775912516803</v>
+        <v>107.0561603261782</v>
       </c>
     </row>
     <row r="13">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>88.33999633789062</v>
+        <v>88.50499725341797</v>
       </c>
     </row>
     <row r="14">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.06153110094139964</v>
+        <v>0.06154830086232971</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.060093867189544</v>
+        <v>1.060103391890992</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>88.33999633789062</v>
+        <v>88.50499725341797</v>
       </c>
     </row>
     <row r="49">
@@ -24592,13 +24592,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>100.7830477604188</v>
+        <v>100.7624758196842</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>157.0174532167475</v>
+        <v>156.9882553382329</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>58.45339790710837</v>
+        <v>58.43925402307212</v>
       </c>
     </row>
     <row r="59">
